--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-07-29T17:14:54.335Z</t>
+    <t>2026-08-05T18:59:55.962Z</t>
   </si>
   <si>
     <t>WKND Trendsetters - Fresh Looks, Bold Stories, Real Life</t>
